--- a/akreditasi/docs/tabel_xlsx/LED/LED-Tabel C4.2 - Penetapan terkait Kebijakan, standar dan indikator terkait.xlsx
+++ b/akreditasi/docs/tabel_xlsx/LED/LED-Tabel C4.2 - Penetapan terkait Kebijakan, standar dan indikator terkait.xlsx
@@ -26,34 +26,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -61,22 +56,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,164 +450,147 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30.35" customWidth="1" min="2" max="2"/>
+    <col width="11.45" customWidth="1" min="3" max="3"/>
+    <col width="10.4" customWidth="1" min="4" max="4"/>
+    <col width="16.7" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dokumen</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>LED — Laporan Evaluasi Diri</t>
-        </is>
-      </c>
+          <t>Tabel C4.2 Penetapan terkait Kebijakan, standar dan indikator terkait implementasi peta jalan PkM, pelibatan mahasiswa berdasarkan visi misi Perguruan Tinggi, UPPS, dan visi keilmuan program studi serta kebutuhan masyarakat dan DUDIKA</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Nomor tabel</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>No.</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>C4.2</t>
-        </is>
-      </c>
+          <t>Referensi</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Indikator</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>IKU/ IKT</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Sasaran/Target</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Nama tabel</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Penetapan terkait Kebijakan, standar dan indikator terkait implementasi peta jalan PkM, pelibatan mahasiswa berdasarkan visi misi Perguruan Tinggi, UPPS, dan visi keilmuan program studi serta kebutuhan masyarakat dan DUDIKA</t>
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>TS-2</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>TS-1</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>TS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Halaman cetak</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>96</v>
-      </c>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Implementasi peta jalan PKM</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Halaman PDF</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Jumlah kolom</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Header tabel</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>No. B1</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Referensi Implementasi peta jalan PKM</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Indikator</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>IKU/ IKT</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Sasaran/Target TS-2</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>TS-1</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>TS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Catatan</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Nomor dan judul dari DAFTAR TABEL LED; posisi tabel dan header kolom dari caption bernomor di badan LED (baris header bertingkat digabung).</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="D2:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>